--- a/Coleta de dados Presenciais.xlsx
+++ b/Coleta de dados Presenciais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mangu\Documents\GitHub\TrabalhoMultiDisciplinar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230A35FB-BBAD-4F01-9EE7-5A7F2807C958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A3CC4D-2210-4445-B59C-5262DF32CBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,12 +32,11 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[hh]:mm"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -49,6 +48,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -72,11 +72,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="46" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -740,6 +741,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -747,7 +749,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1580,7 +1581,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1000"/>
+  <dimension ref="A1:N1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
@@ -1588,39 +1589,63 @@
     <col min="4" max="4" width="27.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="2">
         <v>0.5</v>
       </c>
       <c r="B1" s="3">
         <v>3.472222222222222E-3</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="M1" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N1" s="3">
+        <v>2.0833333333333333E-3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>0.5</v>
       </c>
       <c r="B2" s="3">
         <v>3.5879629629629629E-3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="M2" s="4">
+        <v>0.50694444444444497</v>
+      </c>
+      <c r="N2" s="3">
+        <v>4.1666666666666666E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>0.5</v>
       </c>
       <c r="B3" s="3">
         <v>2.7777777777777779E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="M3" s="4">
+        <v>0.51388888888888895</v>
+      </c>
+      <c r="N3" s="3">
+        <v>5.5555555555555558E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>0.5</v>
       </c>
       <c r="B4" s="3">
         <v>3.1250000000000002E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="M4" s="4">
+        <v>0.52083333333333404</v>
+      </c>
+      <c r="N4" s="3">
+        <v>7.6388888888888886E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>0.5</v>
       </c>
@@ -1628,7 +1653,7 @@
         <v>3.7037037037037038E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>0.5</v>
       </c>
@@ -1636,7 +1661,7 @@
         <v>2.8935185185185184E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>0.5</v>
       </c>
@@ -1644,7 +1669,7 @@
         <v>3.2407407407407406E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>0.5</v>
       </c>
@@ -1652,7 +1677,7 @@
         <v>2.662037037037037E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>0.5</v>
       </c>
@@ -1660,7 +1685,7 @@
         <v>3.2407407407407406E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>0.5</v>
       </c>
@@ -1668,7 +1693,7 @@
         <v>3.1250000000000002E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>0.50694444444444442</v>
       </c>
@@ -1676,7 +1701,7 @@
         <v>7.6388888888888886E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>0.50694444444444442</v>
       </c>
@@ -1684,7 +1709,7 @@
         <v>7.060185185185185E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>0.50694444444444398</v>
       </c>
@@ -1692,7 +1717,7 @@
         <v>7.060185185185185E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>0.50694444444444398</v>
       </c>
@@ -1700,7 +1725,7 @@
         <v>7.7546296296296295E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>0.50694444444444398</v>
       </c>
@@ -1708,7 +1733,7 @@
         <v>7.4074074074074077E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>0.50694444444444398</v>
       </c>
